--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6803NR_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6803NR_SW2.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>Air-Way FF6803 (s37, double-pass 2026-10-15, parts.air-way.com/api/series/37, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p17 FS6803-12-12-12-NWO-FG (ORFS-p017-t03); FORGED part: Air-Way NON-forged row FF6803-12-12-12 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6803 (s37, double-pass 2026-10-15, parts.air-way.com/api/series/37, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p17 FS6803-12-12-12-NWO-FG (ORFS-p017-t03); FORGED part: Air-Way NON-forged row FF6803-12-12-12 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7_1@DRIVE: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "M1 LGTH" = "1.64" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - run leg A1 face -&gt; crossing; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; L7_2@DRIVE: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "M2 LGTH" = "1.64" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - run leg A2 face -&gt; crossing; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; L10@DRIVE: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "N LGTH" = "2.35" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - adjustable stud tip -&gt; crossing; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; S3HEX@HEX: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "C HEX" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - lock nut hex; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "JJ FLATS" = "1.438" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -16 = 1.4375 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "A1 THREAD" "1-7/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -16 = 1.4375 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "A2 THREAD" "1-7/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -16 = 1.3125 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "B THREAD" "1-5/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "A1 THREAD" "1-7/16-12" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "A2 THREAD" "1-7/16-12" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "B THREAD" "1-5/16-12" in the table's format; L11@DRIVE: approved derived (user 2026-10-18 Q-FS-XFER yes): L10@DRIVE 2.35 (Brennan) - Air-Way stud length 0.73 of ORB -16 (L10@DRIVE - L11@DRIVE on every Air-Way row of FS6803 with this ORB dash; Q-FS-ORBSTUD (a) end ORB_FS / NWO_FS); D1_1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6803: FSM -16 bore on 2 Air-Way row(s): 0.81 (unanimous) [Air-Way, not Brennan]; D1_2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6803: FSM -16 bore on 2 Air-Way row(s): 0.81 (unanimous) [Air-Way, not Brennan]; D20@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6803: ORB -16 bore on 1 Air-Way row(s): 0.85 (unanimous) [Air-Way, not Brennan] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7_1@DRIVE: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "M1 LGTH" = "1.64" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - run leg A1 face -&gt; crossing; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; L7_2@DRIVE: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "M2 LGTH" = "1.64" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - run leg A2 face -&gt; crossing; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; L10@DRIVE: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "N LGTH" = "2.35" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - adjustable stud tip -&gt; crossing; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; S3HEX@HEX: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "C HEX" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - lock nut hex; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "JJ FLATS" = "1.438" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.8, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 3/3 rows with an Air-Way value agree to rounding; THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -16 = 1.4375 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "A1 THREAD" "1-7/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -16 = 1.4375 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "A2 THREAD" "1-7/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_N@DRIVE: end library: straight (UN/UNF) thread of dash -16 = 1.3125 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "B THREAD" "1-5/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "A1 THREAD" "1-7/16-12" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "A2 THREAD" "1-7/16-12" in the table's format; $PRP@Thread_N: Brennan ORFS catalog p17 table ORFS-p017-t03 "FS6803-NWO-FG MFS-MFS-MAORB TEE" row FS6803-16-16-16-NWO-FG col "B THREAD" "1-5/16-12" in the table's format; L11@DRIVE: approved derived (user 2026-10-18 Q-FS-XFER yes): L10@DRIVE 2.35 (Brennan) - Air-Way stud length 0.73 of ORB -16 (L10@DRIVE - L11@DRIVE on every Air-Way row of FS6803 with this ORB dash; Q-FS-ORBSTUD (a) end ORB_FS / NWO_FS); D1_1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6803: FSM -16 bore on 2 Air-Way row(s): 0.81 (unanimous) [Air-Way, not Brennan]; D1_2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6803: FSM -16 bore on 2 Air-Way row(s): 0.81 (unanimous) [Air-Way, not Brennan]; D20@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6803: ORB -16 bore on 1 Air-Way row(s): 0.85 (unanimous) [Air-Way, not Brennan] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
